--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106447</v>
+        <v>106528</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106528</v>
+        <v>106534</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106534</v>
+        <v>106536</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106536</v>
+        <v>106537</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106537</v>
+        <v>106543</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106543</v>
+        <v>106547</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106547</v>
+        <v>106549</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106549</v>
+        <v>106551</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106551</v>
+        <v>106564</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106564</v>
+        <v>106566</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106566</v>
+        <v>106570</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106570</v>
+        <v>106590</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106590</v>
+        <v>106591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106599</v>
+        <v>106605</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63054-2025 artfynd.xlsx
+++ b/artfynd/A 63054-2025 artfynd.xlsx
@@ -4791,7 +4791,7 @@
         <v>135229490</v>
       </c>
       <c r="B35" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
